--- a/data/trans_orig/P79$hipoteca_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79$hipoteca_2023-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,67 +760,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8499</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3229</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8878</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>23510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>546</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>34717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>61474</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>56795</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37017</t>
+          <t>45298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63997</t>
+          <t>69849</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>87702</t>
+          <t>102713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>72094</t>
+          <t>85078</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>106634</t>
+          <t>122528</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,67 +1438,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4576</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>10259</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4200</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1381</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>8463</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25524</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>39021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54744</t>
+          <t>65516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>566699</t>
+          <t>609061</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>552570</t>
+          <t>593058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>579756</t>
+          <t>623175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>634630</t>
+          <t>630368</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>619572</t>
+          <t>613481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>652021</t>
+          <t>643957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1201329</t>
+          <t>1239429</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1179018</t>
+          <t>1216133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221659</t>
+          <t>1260266</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,67 +2007,67 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>15349</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>7998</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>24432</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>13840</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>7969</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>21521</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34026</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>29503</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44770</t>
+          <t>53948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18992</t>
+          <t>18978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>22814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>35335</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2537,32 +2537,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>84251</t>
+          <t>94661</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42880</t>
+          <t>75361</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115301</t>
+          <t>116993</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,32 +2572,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>100648</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73528</t>
+          <t>82626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103956</t>
+          <t>120872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>171575</t>
+          <t>195308</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111438</t>
+          <t>168849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205115</t>
+          <t>223024</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -2650,102 +2650,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>8196</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>9173</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>4788</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>18890</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2926</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>7391</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>8193</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>3927</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>15618</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>24457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52494</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42832</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33890</t>
+          <t>37779</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54894</t>
+          <t>62070</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>86279</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50874</t>
+          <t>70711</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98278</t>
+          <t>107105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1054426</t>
+          <t>886131</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1013831</t>
+          <t>860649</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1114206</t>
+          <t>910026</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>795670</t>
+          <t>886162</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>778031</t>
+          <t>862474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>813464</t>
+          <t>905313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1850096</t>
+          <t>1772293</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1805366</t>
+          <t>1738896</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1934350</t>
+          <t>1803284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>15749</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3332,17 +3332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32932</t>
+          <t>28842</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>39515</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,32 +3480,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,27 +3515,27 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>27197</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,32 +3593,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>29443</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3671,69 +3671,69 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17605</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>12813</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>20143</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>11103</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>4172</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>18937</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>27</t>
@@ -3741,32 +3741,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3784,32 +3784,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31944</t>
+          <t>36339</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>56841</t>
+          <t>64135</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3819,32 +3819,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>53408</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>65058</t>
+          <t>69666</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,32 +3854,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>83832</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>113258</t>
+          <t>124096</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -3897,32 +3897,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>708</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,32 +3967,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>25209</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>48296</t>
+          <t>58569</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>38061</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>78915</t>
+          <t>88206</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>589201</t>
+          <t>666940</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>565155</t>
+          <t>643146</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>606063</t>
+          <t>686057</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>831286</t>
+          <t>687694</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>804633</t>
+          <t>669008</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>873746</t>
+          <t>705111</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1420487</t>
+          <t>1354635</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1383099</t>
+          <t>1324473</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1479708</t>
+          <t>1379719</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>39272</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>23452</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>49068</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>36713</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>25859</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>50990</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>71284</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>39703</t>
+          <t>55998</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>67954</t>
+          <t>91816</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4692,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,67 +4727,67 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>14207</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>8346</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>22307</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>13255</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>7329</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>22366</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -4805,32 +4805,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,22 +4840,22 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>36275</t>
+          <t>39870</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>86821</t>
+          <t>104863</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>69463</t>
+          <t>86146</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>106380</t>
+          <t>127398</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,32 +5066,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>125716</t>
+          <t>142902</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>105756</t>
+          <t>122642</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>145501</t>
+          <t>165102</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>212537</t>
+          <t>247765</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>189298</t>
+          <t>220704</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>240436</t>
+          <t>279796</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -5292,22 +5292,22 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,22 +5327,22 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>63145</t>
+          <t>71276</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>47049</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>30240</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>59334</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>101695</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>83072</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>105661</t>
+          <t>119752</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>743564</t>
+          <t>777499</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>718245</t>
+          <t>750500</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>765953</t>
+          <t>802582</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>812735</t>
+          <t>875993</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>790758</t>
+          <t>849009</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>834353</t>
+          <t>898072</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1556298</t>
+          <t>1653492</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1523517</t>
+          <t>1617096</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1586966</t>
+          <t>1687502</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>82,76%</t>
         </is>
       </c>
     </row>
@@ -5713,32 +5713,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5748,32 +5748,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>46623</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>77646</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5826,32 +5826,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>65621</t>
+          <t>85539</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5861,32 +5861,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>48871</t>
+          <t>67680</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>87640</t>
+          <t>105514</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5896,32 +5896,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>90124</t>
+          <t>125300</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>146012</t>
+          <t>178156</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5939,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>40581</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5974,32 +5974,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>26817</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6009,32 +6009,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>58984</t>
+          <t>61950</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -6052,17 +6052,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6087,17 +6087,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6122,17 +6122,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -6165,32 +6165,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>59263</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6200,32 +6200,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>53784</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>64779</t>
+          <t>75265</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>100895</t>
+          <t>114533</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -6278,32 +6278,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>195743</t>
+          <t>261531</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>289261</t>
+          <t>331263</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6313,32 +6313,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>252569</t>
+          <t>322238</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>344051</t>
+          <t>385949</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,32 +6348,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>481189</t>
+          <t>599265</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>618283</t>
+          <t>697938</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6426,67 +6426,67 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>13530</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>33057</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>11330</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>29347</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -6539,22 +6539,22 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6574,22 +6574,22 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6652,67 +6652,67 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
           <t>0,03%</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -6730,32 +6730,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>102394</t>
+          <t>128918</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,32 +6765,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>103192</t>
+          <t>124725</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>149760</t>
+          <t>167612</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>226127</t>
+          <t>271095</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>303138</t>
+          <t>340065</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6843,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2953890</t>
+          <t>2939631</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2895118</t>
+          <t>2894495</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3042585</t>
+          <t>2985086</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3074321</t>
+          <t>3080217</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>3028389</t>
+          <t>3039780</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3148028</t>
+          <t>3117324</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>6028210</t>
+          <t>6019848</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>5945894</t>
+          <t>5961646</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>6138405</t>
+          <t>6077518</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
